--- a/src/main/resources/account/default/BAS-2026---Enskild-firma-K1.xlsx
+++ b/src/main/resources/account/default/BAS-2026---Enskild-firma-K1.xlsx
@@ -427,6 +427,9 @@
           <t>BAS 2026 - Enskild firma K1</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +442,9 @@
           <t>EUBAS97</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -451,6 +457,9 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -461,6 +470,9 @@
       <c r="B4" t="n">
         <v>6</v>
       </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -750,7 +762,11 @@
           <t>Utgående moms, oreducerad</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>7381</t>
